--- a/public/data/eu-steel-trq-flat-dashboard.xlsx
+++ b/public/data/eu-steel-trq-flat-dashboard.xlsx
@@ -7348,12 +7348,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>099832</t>
+          <t>099605</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Viet Nam</t>
+          <t>Other countries</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -7367,16 +7367,16 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>117496.92</v>
+        <v>33338.76</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>21010.94</v>
+        <v>33338.76</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>96485.98</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>17.88</v>
+        <v>100</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -7385,15 +7385,15 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>05-08-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>55.91</v>
+        <v>0</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099832</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099605</t>
         </is>
       </c>
     </row>
@@ -7410,12 +7410,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>099833</t>
+          <t>099836</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>Korea</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -7429,20 +7429,20 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>33783.39</v>
+        <v>26119.93</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>30937.09</v>
+        <v>21424.19</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>2846.3</v>
+        <v>4695.74</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>91.56999999999999</v>
+        <v>82.02</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -7451,11 +7451,11 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099833</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099836</t>
         </is>
       </c>
     </row>
@@ -7472,12 +7472,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>099834</t>
+          <t>099832</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Turkiye</t>
+          <t>Viet Nam</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -7491,16 +7491,16 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>63925.33</v>
+        <v>117496.92</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>63925.33</v>
+        <v>21010.94</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
+        <v>96485.98</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>100</v>
+        <v>17.88</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -7509,15 +7509,15 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>30-07-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>55.91</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099834</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099832</t>
         </is>
       </c>
     </row>
@@ -7534,12 +7534,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>099835</t>
+          <t>099833</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -7553,33 +7553,33 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>58295.85</v>
+        <v>33783.39</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>24757.28</v>
+        <v>30937.09</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>33538.57</v>
+        <v>2846.3</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>42.47</v>
+        <v>91.56999999999999</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>382.91</v>
+        <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099835</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099833</t>
         </is>
       </c>
     </row>
@@ -7596,12 +7596,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>099836</t>
+          <t>099834</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Korea</t>
+          <t>Turkiye</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -7615,16 +7615,16 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>26119.93</v>
+        <v>63925.33</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>21424.19</v>
+        <v>63925.33</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>4695.74</v>
+        <v>0</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>82.02</v>
+        <v>100</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -7633,15 +7633,15 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>30-07-2026</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099836</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099834</t>
         </is>
       </c>
     </row>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>099505</t>
+          <t>099835</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FTA Quota - CSQ</t>
+          <t>India</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -7677,16 +7677,16 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>38881.49</v>
+        <v>58295.85</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>38881.49</v>
+        <v>24757.28</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
+        <v>33538.57</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>100</v>
+        <v>42.47</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -7695,15 +7695,15 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>22-07-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>382.91</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099505</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099835</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>099605</t>
+          <t>099505</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Other countries</t>
+          <t>FTA Quota - CSQ</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -7739,10 +7739,10 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>33338.76</v>
+        <v>38881.49</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>33338.76</v>
+        <v>38881.49</v>
       </c>
       <c r="I8" s="2" t="n">
         <v>0</v>
@@ -7757,7 +7757,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>05-08-2026</t>
+          <t>22-07-2026</t>
         </is>
       </c>
       <c r="M8" t="n">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099605</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099505</t>
         </is>
       </c>
     </row>
@@ -7782,12 +7782,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>099714</t>
+          <t>099718</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FTA Quota - Other countries</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -7801,33 +7801,33 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>12761.32</v>
+        <v>11600.08</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>12761.32</v>
+        <v>11454.32</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0</v>
+        <v>145.76</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>100</v>
+        <v>98.73999999999999</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>14-08-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>44.09</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099714</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099718</t>
         </is>
       </c>
     </row>
@@ -7844,12 +7844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>099718</t>
+          <t>099716</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -7863,16 +7863,16 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>11600.08</v>
+        <v>2874.21</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>11454.32</v>
+        <v>2873.59</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>145.76</v>
+        <v>0.62</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>98.73999999999999</v>
+        <v>99.98</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -7881,15 +7881,15 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>44.09</v>
+        <v>0</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099718</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099716</t>
         </is>
       </c>
     </row>
@@ -7906,12 +7906,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>099716</t>
+          <t>099715</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -7925,25 +7925,25 @@
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>2874.21</v>
+        <v>2943.83</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>2873.59</v>
+        <v>2943.83</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>99.98</v>
+        <v>100</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>21-08-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099716</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099715</t>
         </is>
       </c>
     </row>
@@ -7968,12 +7968,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>099715</t>
+          <t>099717</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -7987,10 +7987,10 @@
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>2943.83</v>
+        <v>3150.34</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>2943.83</v>
+        <v>3150.34</v>
       </c>
       <c r="I12" s="2" t="n">
         <v>0</v>
@@ -8013,7 +8013,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099715</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099717</t>
         </is>
       </c>
     </row>
@@ -8030,12 +8030,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>099717</t>
+          <t>099714</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>FTA Quota - Other countries</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -8049,10 +8049,10 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>3150.34</v>
+        <v>12761.32</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>3150.34</v>
+        <v>12761.32</v>
       </c>
       <c r="I13" s="2" t="n">
         <v>0</v>
@@ -8067,7 +8067,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>21-08-2026</t>
+          <t>14-08-2026</t>
         </is>
       </c>
       <c r="M13" t="n">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099717</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099714</t>
         </is>
       </c>
     </row>
